--- a/协作/09-需求契约草稿.xlsx
+++ b/协作/09-需求契约草稿.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -595,10 +595,74 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>高</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>契约-0004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>验收-0005</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>协议默认全角色全开、零配置，本仓库 37+3 交付物全部在档</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>无档位/无开关/无可选项；偏离只能记账本并在 G8 前关闭</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>契约-0005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>验收-0006</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>对外交付包 v3.5 可交付，归档快照可校验可还原</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>包不含本仓库真实验收编号与账本历史</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
@@ -606,10 +670,10 @@
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation sqref="F2:F121" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值不合法" error="只能选择下拉里的值" type="list">
+    <dataValidation sqref="F2:F121" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"草稿,已提交"</formula1>
     </dataValidation>
-    <dataValidation sqref="E2:E121" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值不合法" error="只能选择下拉里的值" type="list">
+    <dataValidation sqref="E2:E121" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"高,中,低"</formula1>
     </dataValidation>
   </dataValidations>

--- a/协作/09-需求契约草稿.xlsx
+++ b/协作/09-需求契约草稿.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -663,6 +663,38 @@
         </is>
       </c>
       <c r="F6" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>契约-0006</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>验收-0008</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>DCG 版本库不含协议与模板，按 TEAMODEL 仓库 tag tm-v3.5.1 引用</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>模板作为本地缓存不入库；协议升版需同步 01 画像的版本号与标签</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>

--- a/协作/09-需求契约草稿.xlsx
+++ b/协作/09-需求契约草稿.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -695,6 +695,38 @@
         </is>
       </c>
       <c r="F7" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>契约-0007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>验收-0009</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>README 标题为 # DCG、不含 v2 状态段、§0 为适配场景</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>只改 README，不动代码与契约文件</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>

--- a/协作/09-需求契约草稿.xlsx
+++ b/协作/09-需求契约草稿.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -727,6 +727,38 @@
         </is>
       </c>
       <c r="F8" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>契约-0008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>验收-0010</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>README 定位按用户口径修订（JSONata 描述语言 / 编译固化 / 主场景任意数据结构转换）</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>只改 README 首段与 §0，不动代码与契约文件</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>

--- a/协作/09-需求契约草稿.xlsx
+++ b/协作/09-需求契约草稿.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -759,6 +759,38 @@
         </is>
       </c>
       <c r="F9" t="inlineStr">
+        <is>
+          <t>已提交</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>契约-0009</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>验收-0011</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>README 删除基线/锚点引用块与 §0.1–§0.3 三个子节</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>只改 README，不动代码与契约文件</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
         <is>
           <t>已提交</t>
         </is>
